--- a/nursing/フォーマット/02_訪問看護記録様式/06_訪問看護記録書Ⅰ（フェイスシート）.xlsx
+++ b/nursing/フォーマット/02_訪問看護記録様式/06_訪問看護記録書Ⅰ（フェイスシート）.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="訪問看護記録書I" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="フェイスシート" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,18 @@
     <font>
       <name val="Meiryo UI"/>
       <b val="1"/>
+      <color rgb="FFDC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
       <sz val="9"/>
     </font>
     <font>
@@ -44,10 +56,16 @@
       <name val="Meiryo UI"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -56,16 +74,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF0E7490"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCFFAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E7490"/>
+        <fgColor rgb="FFF8FAFC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -79,28 +102,67 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -468,365 +530,860 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>訪問看護記録書Ⅰ（基本情報・フェイスシート）</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>【保管義務】完結の日から5年間保管。状態変化・療養環境変化時に随時更新すること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>【基本情報】</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>利用者氏名（ふりがな）</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>（　　　　　　　　）</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>生年月日</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　年　月　日生（　歳）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>性別</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>男 ・ 女</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>要介護認定</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">なし / 要支援　 / 要介護　</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>障害の種別</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>身体・精神・知的・難病・その他</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>（　　　　　　　　　　　　　　　）様</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>生年月日・年齢</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　年　月　日生（　　歳）　男 ・ 女</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>住所・電話番号</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>〒　　－　　　　　TEL：</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>主傷病名（主たる傷病）</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>副傷病名・合併症</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>現病歴（発症経緯・経過・現在の状態）</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>例）〇年〇月に脳梗塞発症、左片麻痺残存。現在外来リハ継続中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>既往歴（手術歴・入院歴・重要な病歴）</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>例）H25年 大腸がん手術（人工肛門造設）、糖尿病10年</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>アレルギー（薬剤・食品・その他）</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>なし / あり（　　　　　　　　　　）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>感染症・注意事項</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>なし / あり（　　　　　　　　　　）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>【保険・認定情報】</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>保険の種類</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>健康保険 / 国民健康保険 / 後期高齢者医療 / 自立支援医療（精神通院） / その他（　　）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>自立支援医療 受給者証番号</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>なし / あり（番号：　　　　　　　上限月額：　　　円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>要介護認定区分</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>なし / 要支援（　）/ 要介護（　）  認定日：　　年　月　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>障害支援区分</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>区分　　　/手帳等級：</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>住所</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>〒</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>電話番号</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>主傷病名・診断名</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>副傷病名</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>主治医氏名・医療機関</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>電話番号</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>緊急連絡先①（氏名・続柄）</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>電話（日中）</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>緊急連絡先②（氏名・続柄）</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>電話（夜間）</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>なし / 区分（　）  認定日：　　年　月　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>身体障害者手帳</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>なし / あり（　　級・種別：　　　　）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>精神障害者保健福祉手帳</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>なし / あり（　　級）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>訪問看護指示書 有効期限</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　年　月　日まで　　　　医療機関名：</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>【主治医・医療機関情報】</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>主治医氏名・診療科</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>医療機関名・所在地</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>医療機関 電話番号</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>TEL：　　　　　　　　　  FAX：</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>訪問看護の依頼目的</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>例）褥瘡処置・服薬管理・リハビリ・精神科訪問看護・ターミナルケア</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>訪問頻度（指示内容）</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>週　　回　時間/回　担当職種：看護師 / 准看護師 / PT / OT / ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>【緊急連絡先・関係機関】</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>緊急連絡先①（続柄・氏名）</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　続柄：　　　　　氏名：　　　　　TEL（日中）：　　　　TEL（夜間）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>緊急連絡先②（続柄・氏名）</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　続柄：　　　　　氏名：　　　　　TEL（日中）：　　　　TEL（夜間）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>緊急搬送先病院</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　医療機関名：　　　　　　　　　　TEL：　　　　　　　　（主治医の指定先）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>担当相談支援専門員</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>事業所・電話</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>氏名：　　　　　　　　　事業所：　　　　　　　　TEL：</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>ケアマネジャー（介護保険）</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>事業所・電話</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>保険の種類</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>健保 / 国保 / 後期高齢 / その他</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>訪問看護指示書有効期限</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　月　日まで</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>自立支援医療（精神通院）</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>あり（上限月額：　　　円） / なし</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>受給者証番号</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>アレルギー</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>感染症・注意事項</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>ADL・機能レベル</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>認知機能</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>【医療処置内容（現在実施中のもの）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>氏名：　　　　　　　　　事業所：　　　　　　　　TEL：</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>居宅介護支援事業所</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>事業所名：　　　　　　　　　　　　TEL：</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>その他関係機関（デイ・訪介等）</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>【生活状況・療養環境】</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>居住形態</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>一人暮らし / 家族と同居 / グループホーム / 施設（　　　　　　）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>住環境・バリアフリー</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>戸建て / マンション　エレベーター：あり/なし　段差：あり/なし  その他：</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>主な介護者</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>氏名：　　　　　　続柄：　　　　　介護力：良好 / 不十分 / なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>生活歴（仕事歴・趣味・習慣）</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>例）元会社員、趣味は読書・囲碁、毎朝散歩の習慣あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>本人の療養・生活に対する意向</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>例）「できるだけ家にいたい」「家族に迷惑をかけたくない」</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>家族の介護・療養に対する意向</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>【ADL評価（Barthel Index 準拠）】　　評価日：　　年　月　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>自立/介助</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>状況の詳細</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>前回評価</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>変化</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>食事</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>自立/一部介助/全介助</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr"/>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>移乗</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>自立/一部介助/全介助</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr"/>
+      <c r="D45" s="5" t="inlineStr"/>
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>整容</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>自立/介助</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr"/>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>トイレ動作</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>自立/一部介助/全介助</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr"/>
+      <c r="D47" s="5" t="inlineStr"/>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>入浴</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>自立/介助</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr"/>
+      <c r="D48" s="5" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>歩行</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>自立/補装具/介助/車椅子</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr"/>
+      <c r="D49" s="5" t="inlineStr"/>
+      <c r="E49" s="5" t="inlineStr"/>
+      <c r="F49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>階段</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>自立/介助/不可</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr"/>
+      <c r="D50" s="5" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>更衣</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>自立/一部介助/全介助</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr"/>
+      <c r="D51" s="5" t="inlineStr"/>
+      <c r="E51" s="5" t="inlineStr"/>
+      <c r="F51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>排便コントロール</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>自立/時々失禁/常に失禁</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr"/>
+      <c r="D52" s="5" t="inlineStr"/>
+      <c r="E52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>排尿コントロール</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>自立/時々失禁/常に失禁</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr"/>
+      <c r="D53" s="5" t="inlineStr"/>
+      <c r="E53" s="5" t="inlineStr"/>
+      <c r="F53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>【認知機能・意思疎通・精神状態】</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>認知症の有無・程度</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>なし / 軽度 / 中等度 / 重度　日常生活自立度：Ⅰ/Ⅱa/Ⅱb/Ⅲa/Ⅲb/Ⅳ/M</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>意思疎通の状況</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>良好 / やや困難 / 困難（コミュニケーション方法：　　　　　　　　　　）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>精神状態・情動</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>安定 / 不安定（内容：　　　　　　　　　　　　　　　　　　　　　　　）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>睡眠状況</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>良好 / 不良（　　時間程度　中途覚醒：あり/なし　睡眠薬：あり/なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>【医療処置・医療機器管理】</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n"/>
+      <c r="C59" s="8" t="n"/>
+      <c r="D59" s="8" t="n"/>
+      <c r="E59" s="8" t="n"/>
+      <c r="F59" s="8" t="n"/>
+      <c r="G59" s="8" t="n"/>
+      <c r="H59" s="8" t="n"/>
+      <c r="I59" s="8" t="n"/>
+      <c r="J59" s="9" t="n"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>例）気管切開・吸引（1日　回）　人工呼吸器（　　）　経管栄養（NG/胃ろう/腸ろう）　留置カテーテル　輸液（　）　褥瘡処置（　部位）　点滴</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="55" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>【服薬管理・処方薬一覧】</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>【特記事項・家族への指導事項】</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>作成日：　　年　月　日　担当看護師：　　　　　　　　最終更新日：　　年　月　日</t>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>例）降圧薬（　　）朝1錠、血糖降下薬（　　）毎食後、抗精神病薬（　　）就寝前　→ 服薬管理：自己管理/一包化/ヘルパー管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="50" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>【特記事項・支援上の注意点】</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>例）水分摂取が少ない傾向あり（誤嚥リスク）。右足に浮腫あり。家族への指導事項：体位変換2時間毎の励行</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作成日：　　年　月　日　担当看護師（署名）：　　　　　　　　　最終更新日：　　年　月　日　更新者：　　　　　　　　</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
+  <mergeCells count="92">
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="D56:J56"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="D24:J24"/>
+    <mergeCell ref="D33:J33"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A63:J63"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D26:J26"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D19:J19"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D37:J37"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D39:J39"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D15:J15"/>
+    <mergeCell ref="D29:J29"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="D23:J23"/>
+    <mergeCell ref="D38:J38"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A60:J60"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="D57:J57"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="D17:J17"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A62:J62"/>
+    <mergeCell ref="D25:J25"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D55:J55"/>
+    <mergeCell ref="D30:J30"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D14:J14"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A59:J59"/>
+    <mergeCell ref="A64:J64"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D31:J31"/>
+    <mergeCell ref="D40:J40"/>
+    <mergeCell ref="A61:J61"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A54:J54"/>
+    <mergeCell ref="D32:J32"/>
+    <mergeCell ref="D41:J41"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D16:J16"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="D18:J18"/>
+    <mergeCell ref="D58:J58"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D20:J20"/>
+    <mergeCell ref="D34:J34"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="D36:J36"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A21:J21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
